--- a/src/test/resources/testdata/HealthCareTestData.xlsx
+++ b/src/test/resources/testdata/HealthCareTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\areti\eclipse-workspace1\HealthcareAutomation\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\areti\eclipse-workspace1\HealthcareAutomation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28173AE-7490-4CF1-95C5-1FBF0B98DE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD19898-2D1C-4DE4-B4CD-4F10FB465D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>John Doe</t>
   </si>
@@ -98,6 +98,15 @@
   </si>
   <si>
     <t>reAdmission</t>
+  </si>
+  <si>
+    <t>expectedResult</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Failure</t>
   </si>
 </sst>
 </file>
@@ -423,43 +432,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>15</v>
       </c>
       <c r="B1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
